--- a/Hydrocare_near_final.xlsx
+++ b/Hydrocare_near_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alireza.mohammadshafie/Documents/hydrocare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F2906D1-A10B-6841-AA8D-5E596C4277DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B36CAC6-2DB6-7C44-954B-9D49D2DE1BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -555,6 +555,7 @@
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
     <col min="10" max="10" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
